--- a/마이밍_IA_문서.xlsx
+++ b/마이밍_IA_문서.xlsx
@@ -1285,8 +1285,8 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>readCNArticle()
-earn()</t>
+          <t>earn() 직접 호출
+(TODO: 광고 SDK 콜백으로 교체)</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="78" customHeight="1">
+    <row r="4" ht="104" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>CardNews
@@ -2178,12 +2178,14 @@
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>String id, title, summary
+          <t>String id, headline, summary, content
 NewsCategory category
 NewsTier tier
-List&lt;String&gt; pages
-int reward
-bool isRead</t>
+String emoji, stat, time
+List&lt;String&gt; keywords
+int likes, bookmarks
+bool isNew, isRead
+bool isLiked, isBookmarked</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
@@ -2556,7 +2558,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="78" customHeight="1">
+    <row r="10" ht="91" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
           <t>addSteps()</t>
@@ -2570,7 +2572,8 @@
       <c r="C10" s="10" t="inlineStr">
         <is>
           <t>steps += count
-rate = hasManhwaBoost ? 1.5x : 1x
+rate = hasManhwaBoost ? 0.015 : 0.01
+(10,000보 = ₩150 부스트 / ₩100 기본)
 walletAmount += count * rate
 addLedger()
 notifyListeners()

--- a/마이밍_IA_문서.xlsx
+++ b/마이밍_IA_문서.xlsx
@@ -1656,7 +1656,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
+    <row r="23" ht="78" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
           <t>SP-01</t>
@@ -1685,11 +1685,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>TabBar ×8
+          <t>_DwellTimeCard (체류 시간 카드)
+잔액 표시 배너
+TabBar ×8
 (부스터/이용권/상품권/주거/식음료/뷰티/디지털/기타)
 _ShopItemList
-_ShopItemCard ×19
-잔액 표시 배너</t>
+_ShopItemCard ×19</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1702,7 +1703,9 @@
           <t>walletAmount
 buyBooster()
 spend()
-hasManhwaBoost</t>
+hasManhwaBoost
+firstAccessDate
+totalSecondsWithCurrent</t>
         </is>
       </c>
       <c r="I23" s="8" t="inlineStr">
@@ -2122,7 +2125,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="130" customHeight="1">
+    <row r="3" ht="169" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>AppState
@@ -2145,7 +2148,10 @@
 int cnReadCount
 bool cnMissionDone
 List&lt;LedgerEntry&gt; ledger
-String? lastAttendanceDate</t>
+String? lastAttendanceDate
+String? firstAccessDate
+int totalSecondsInApp
+DateTime? _sessionStart (runtime)</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -2305,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2591,58 +2597,181 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1">
+    <row r="11" ht="52" customHeight="1">
       <c r="A11" s="18" t="inlineStr">
         <is>
+          <t>startSession()</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>void startSession()</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>firstAccessDate ??= 오늘 날짜 (최초 1회)
+_sessionStart ??= DateTime.now()
+⚠ totalSecondsInApp은 저장하지 않음
+→ 앱 종료(kill) 시 자동 초기화</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>main.dart
+(initState + AppLifecycleState.resumed)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>firstAccessDate만 저장</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>pauseSession()</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>void pauseSession()</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>totalSecondsInApp += 경과 초
+_sessionStart = null
+백그라운드 전환 시 호출
+앱 재시작 후 totalSecondsInApp = 0</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>main.dart
+(AppLifecycleState.paused / dispose)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>저장 안 함 (세션 한정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>currentSessionSeconds</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>int get currentSessionSeconds</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>_sessionStart == null → 0
+그 외: DateTime.now().difference(_sessionStart).inSeconds</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>SP-01 _DwellTimeCard</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>totalSecondsWithCurrent</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>int get totalSecondsWithCurrent</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>totalSecondsInApp + currentSessionSeconds
+앱 재시작 후엔 totalSecondsInApp=0
+→ = currentSessionSeconds</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>SP-01 _DwellTimeCard</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
           <t>loadFromPrefs()</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Future&lt;void&gt; loadFromPrefs()</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>SharedPreferences에서 전체 상태 복원
-notifyListeners()</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+notifyListeners()
+⚠ totalSecondsInApp은 로드 안 함
+→ 앱 시작마다 0으로 초기화</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>main.dart (앱 시작)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>읽기 전용</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>saveToPrefs()</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Future&lt;void&gt; saveToPrefs()</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>steps, wallet, 부스터 플래그 4종
-cnRead, cnMission, attendance 저장</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
+cnRead, cnMission, attendance 저장
+firstAccessDate 저장
+⚠ totalSecondsInApp은 저장 안 함</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>earn/spend/buyBooster/addSteps
-readCNArticle 후 자동 호출 (fire-and-forget)</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
+startSession 후 자동 호출</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>쓰기</t>
         </is>

--- a/마이밍_IA_문서.xlsx
+++ b/마이밍_IA_문서.xlsx
@@ -1093,9 +1093,9 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>출석체크 버튼
-광고 보너스
-행운 뽑기</t>
+          <t>출석체크 버튼 (달력 팝업 포함)
+광고 보너스 (→ 카드뉴스 탭 이동)
+행운 뽑기 (10~100원 랜덤)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1106,12 +1106,14 @@
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>canAttendToday
-earn()</t>
+attendanceDates
+earn()
+switchToCardNewsTab()</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>→ CardNewsPage (탭 전환)</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
@@ -1213,7 +1215,7 @@
           <t>_CatChip ×5 (카테고리 필터)
 _SectionHeader
 _Top3Card (일간 TOP3)
-_WeeklyCard (주간)
+_WeeklyCard (주간, 카드 전체 클릭 가능)
 _ReactBtn</t>
         </is>
       </c>
@@ -2125,7 +2127,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="169" customHeight="1">
+    <row r="3" ht="195" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
           <t>AppState
@@ -2149,6 +2151,8 @@
 bool cnMissionDone
 List&lt;LedgerEntry&gt; ledger
 String? lastAttendanceDate
+List&lt;String&gt; attendanceDates (달력용)
+int cardNewsTabTrigger
 String? firstAccessDate
 int totalSecondsInApp
 DateTime? _sessionStart (runtime)</t>
@@ -2311,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2508,7 +2512,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="39" customHeight="1">
+    <row r="8" ht="52" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>doAttendance()</t>
@@ -2523,6 +2527,7 @@
         <is>
           <t>canAttendToday=false면 즉시 return
 lastAttendanceDate = 오늘
+attendanceDates에 오늘 날짜 추가
 earn(+₩10)</t>
         </is>
       </c>
@@ -2716,62 +2721,92 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
+          <t>switchToCardNewsTab()</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>void switchToCardNewsTab()</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>cardNewsTabTrigger++ → notifyListeners()
+MainShell이 감지해 카드뉴스 탭(index 1)으로 전환</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>H-03 광고보너스 탭</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="65" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
           <t>loadFromPrefs()</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Future&lt;void&gt; loadFromPrefs()</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>SharedPreferences에서 전체 상태 복원
+attendanceDates 로드 (getStringList)
 notifyListeners()
 ⚠ totalSecondsInApp은 로드 안 함
 → 앱 시작마다 0으로 초기화</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>main.dart (앱 시작)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>읽기 전용</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+    <row r="17" ht="65" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>saveToPrefs()</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Future&lt;void&gt; saveToPrefs()</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>steps, wallet, 부스터 플래그 4종
 cnRead, cnMission, attendance 저장
+attendanceDates (전체 출석 날짜 목록) 저장
 firstAccessDate 저장
 ⚠ totalSecondsInApp은 저장 안 함</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>earn/spend/buyBooster/addSteps
 startSession 후 자동 호출</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>쓰기</t>
         </is>

--- a/마이밍_IA_문서.xlsx
+++ b/마이밍_IA_문서.xlsx
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1305,38 +1305,103 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>🎮 게임 탭 (Tab 2)</t>
+          <t>📰 카드뉴스 · SPA 전용</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>N-03</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>adVideoListPage
+광고보고 기사읽기</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>/adVideoList</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>H-03 (광고 보너스)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>미션 배너 (읽은 기사 카운터)
+CARD_NEWS 기반 기사 그리드
+watchAdAndOpenArticle(id)
+earnCN(id)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>CARD_NEWS</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>STATE.reads
+playFullscreenAd()
+openCNArticle()</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>SPA only — Flutter 미구현</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>마이밍_만보기버전.html (adVideoListPage)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>🎮 게임 탭 (Tab 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>G-01</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>GameSelectPage
 게임 선택 2×4 그리드</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>/game-select</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>MainShell Tab 2</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Tab 2</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>2×4 GridView
 게임 카드 ×8
@@ -1344,17 +1409,17 @@
 개발예정 스낵바</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>walletAmount</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>→ BrickGamePage
 → JumpGamePage
@@ -1364,40 +1429,40 @@
 (개발예정: puzzle·quiz·shooting·card)</t>
         </is>
       </c>
-      <c r="J16" s="9" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>pages/game/game_select_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>G-02</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>BrickGamePage
 벽돌깨기 (Flame)</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>push (G-01)</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>GameWidget&lt;BrickGame&gt;
 _ResultOverlay
@@ -1405,56 +1470,56 @@
 패들 드래그</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>earn()</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>← pop
 보상: min(score÷10, 200)</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>game/games/brick_game_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>G-03</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>JumpGamePage
 무한점프 (Flame)</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>push (G-01)</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>GameWidget&lt;JumpGame&gt;
 TapCallbacks
@@ -1462,112 +1527,112 @@
 코인 수집</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>earn()</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>← pop
 보상: min(dist÷20+coins×5, 150)</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>game/games/jump_game_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21" ht="39" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>G-04</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>CatchGamePage
 낚시대전 (Flame)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>push (G-01)</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>GameWidget&lt;CatchGame&gt;
 드래그 조작
 🐟+10 🪙+15 💣-10</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>earn()</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>← pop
 보상: min(score÷15, 100)</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>game/games/catch_game_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>G-05</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>SnakeGamePage
 뱀게임 (CustomPainter)</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>push (G-01)</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>Stack → Column + Positioned.fill
 CustomPaint (_SnakePainter)
@@ -1575,117 +1640,117 @@
 스와이프 GestureDetector</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>earn()</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>← pop
 보상: min(score×3, 150)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>game/games/snake_game_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>G-06</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>GlobalRankPage
 전체 랭킹</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>/rank</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>push (G-01)</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>ListView (_RankEntry ×10)
 TOP3 강조 (👑🥈🥉)</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>← pop</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>pages/game/global_rank_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>🎁 교환소 (Shop)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="78" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25" ht="78" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>SP-01</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>ShopPage
 적립금 교환소</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>/shop</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>push (H-01/N-01)</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>_DwellTimeCard (체류 시간 카드)
 잔액 표시 배너
@@ -1695,12 +1760,12 @@
 _ShopItemCard ×19</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>walletAmount
 buyBooster()
@@ -1710,52 +1775,52 @@
 totalSecondsWithCurrent</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>← pop</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J25" s="13" t="inlineStr">
         <is>
           <t>pages/shop/shop_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>🎯 고정비 절감 미션 (Offerwall)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>OW-01</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>OfferwallPage
 29개 절감 미션</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>/offerwall</t>
         </is>
       </c>
-      <c r="D25" s="10" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>push (H-01/H-04)</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>_CatChip ×9 (카테고리)
 _TypeTab ×4 (전체/추천/간단/고보상)
@@ -1764,66 +1829,66 @@
 배너 그라디언트</t>
         </is>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Offer
 OfferCategory
 OfferType</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>walletAmount
 earn()</t>
         </is>
       </c>
-      <c r="I25" s="12" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>BottomSheet → _OfferModal
 ← pop</t>
         </is>
       </c>
-      <c r="J25" s="13" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>pages/offerwall/offerwall_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>📋 고정비 관리 (Bill)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="91" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="29" ht="91" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>B-01</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>BillPage
 청구서 목록</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>/bill</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>push (H-01/H-04)</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
         <is>
           <t>월간 합계 헤더
 절감 진행바
@@ -1834,67 +1899,67 @@
 _BillFormSheet</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G29" s="10" t="inlineStr">
         <is>
           <t>Bill
 BillType</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>walletAmount
 spend()
 ledger</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>BottomSheet → _BillFormSheet
 탭 전환 → _LedgerTab
 ← pop</t>
         </is>
       </c>
-      <c r="J27" s="9" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>pages/bill/bill_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>🔮 오늘의 운세 (Fortune)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>F-01</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>FortunePage
 운세 조회</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>/fortune</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>push (H-01)</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>_FormView (생년월일·성별·시)
 _ResultView
@@ -1902,62 +1967,62 @@
 _FortuneStat ×4</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>earn() (+₩5)</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>← pop</t>
         </is>
       </c>
-      <c r="J29" s="13" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>pages/fortune/fortune_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>🎟 쿠폰함 (Coupon)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>C-01</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>CouponPage
 보유 쿠폰 목록</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>/coupon</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>push (H-01)</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>쿠폰 카드 목록
 D-Day 뱃지
@@ -1965,62 +2030,62 @@
 Clipboard.setData()</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>← pop</t>
         </is>
       </c>
-      <c r="J31" s="9" t="inlineStr">
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>pages/coupon/coupon_page.dart</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>👤 내 정보 (Profile)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="52" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>P-01</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>ProfilePage
 사용자 정보·내역</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>/profile</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>push (H-01 앱바)</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>프로필 편집 영역
 _StatTile ×2 (적립금/절감)
@@ -2028,38 +2093,39 @@
 _SettingItem 목록</t>
         </is>
       </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>walletAmount
 ledger
 steps</t>
         </is>
       </c>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>→ /shop
 ← pop</t>
         </is>
       </c>
-      <c r="J33" s="13" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>pages/profile/profile_page.dart</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A15:J15"/>
@@ -2918,12 +2984,13 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>min(score ÷ 10, 200)</t>
+          <t>Flutter: min(score ÷ 10, 200)
+SPA: 레벨별 earn(lv1:₩15~lv10:₩90)</t>
         </is>
       </c>
       <c r="G3" s="26" t="inlineStr">
         <is>
-          <t>₩200</t>
+          <t>Flutter:₩200 / SPA:₩90</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -2995,7 +3062,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>좌우 드���그</t>
+          <t>좌우 드래그</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
